--- a/excel/1000(n)/ReverseSort_Dataset.xlsx
+++ b/excel/1000(n)/ReverseSort_Dataset.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="28">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -222,67 +222,67 @@
         <v>1000.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>3094100.0</v>
+        <v>314200.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>681800.0</v>
+        <v>351500.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>776100.0</v>
+        <v>669700.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>651400.0</v>
+        <v>598900.0</v>
       </c>
       <c r="G2" t="n" s="0">
-        <v>324500.0</v>
+        <v>594800.0</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>707700.0</v>
+        <v>606300.0</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>806900.0</v>
+        <v>665200.0</v>
       </c>
       <c r="J2" t="n" s="0">
-        <v>606700.0</v>
+        <v>594700.0</v>
       </c>
       <c r="K2" t="n" s="0">
-        <v>675600.0</v>
+        <v>594600.0</v>
       </c>
       <c r="L2" t="n" s="0">
-        <v>596600.0</v>
+        <v>651900.0</v>
       </c>
       <c r="M2" t="n" s="0">
-        <v>596000.0</v>
+        <v>594500.0</v>
       </c>
       <c r="N2" t="n" s="0">
-        <v>603300.0</v>
+        <v>332000.0</v>
       </c>
       <c r="O2" t="n" s="0">
-        <v>558900.0</v>
+        <v>612100.0</v>
       </c>
       <c r="P2" t="n" s="0">
-        <v>711500.0</v>
+        <v>608300.0</v>
       </c>
       <c r="Q2" t="n" s="0">
-        <v>597800.0</v>
+        <v>606400.0</v>
       </c>
       <c r="R2" t="n" s="0">
-        <v>599600.0</v>
+        <v>647200.0</v>
       </c>
       <c r="S2" t="n" s="0">
-        <v>888200.0</v>
+        <v>818200.0</v>
       </c>
       <c r="T2" t="n" s="0">
-        <v>510300.0</v>
+        <v>598300.0</v>
       </c>
       <c r="U2" t="n" s="0">
-        <v>606400.0</v>
+        <v>594200.0</v>
       </c>
       <c r="V2" t="n" s="0">
-        <v>810300.0</v>
+        <v>642800.0</v>
       </c>
       <c r="W2" t="n" s="0">
-        <v>770185.0</v>
+        <v>584790.0</v>
       </c>
     </row>
     <row r="3">
@@ -293,67 +293,67 @@
         <v>1000.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>1846600.0</v>
+        <v>93100.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>666100.0</v>
+        <v>160000.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>1911800.0</v>
+        <v>150700.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>424600.0</v>
+        <v>84900.0</v>
       </c>
       <c r="G3" t="n" s="0">
-        <v>96900.0</v>
+        <v>86100.0</v>
       </c>
       <c r="H3" t="n" s="0">
-        <v>151500.0</v>
+        <v>91100.0</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>108500.0</v>
+        <v>118500.0</v>
       </c>
       <c r="J3" t="n" s="0">
-        <v>90100.0</v>
+        <v>87400.0</v>
       </c>
       <c r="K3" t="n" s="0">
-        <v>170700.0</v>
+        <v>87200.0</v>
       </c>
       <c r="L3" t="n" s="0">
-        <v>87000.0</v>
+        <v>87400.0</v>
       </c>
       <c r="M3" t="n" s="0">
-        <v>86700.0</v>
+        <v>88400.0</v>
       </c>
       <c r="N3" t="n" s="0">
-        <v>86800.0</v>
+        <v>109700.0</v>
       </c>
       <c r="O3" t="n" s="0">
+        <v>89300.0</v>
+      </c>
+      <c r="P3" t="n" s="0">
+        <v>85200.0</v>
+      </c>
+      <c r="Q3" t="n" s="0">
         <v>87700.0</v>
       </c>
-      <c r="P3" t="n" s="0">
-        <v>94900.0</v>
-      </c>
-      <c r="Q3" t="n" s="0">
-        <v>86300.0</v>
-      </c>
       <c r="R3" t="n" s="0">
-        <v>85400.0</v>
+        <v>181800.0</v>
       </c>
       <c r="S3" t="n" s="0">
-        <v>122900.0</v>
+        <v>87600.0</v>
       </c>
       <c r="T3" t="n" s="0">
-        <v>99400.0</v>
+        <v>92700.0</v>
       </c>
       <c r="U3" t="n" s="0">
-        <v>193100.0</v>
+        <v>87200.0</v>
       </c>
       <c r="V3" t="n" s="0">
-        <v>89200.0</v>
+        <v>97100.0</v>
       </c>
       <c r="W3" t="n" s="0">
-        <v>329310.0</v>
+        <v>102655.0</v>
       </c>
     </row>
     <row r="4">
@@ -364,67 +364,67 @@
         <v>1000.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>2390800.0</v>
+        <v>1172800.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>888800.0</v>
+        <v>896500.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>825900.0</v>
+        <v>995600.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>918900.0</v>
+        <v>831100.0</v>
       </c>
       <c r="G4" t="n" s="0">
-        <v>1102800.0</v>
+        <v>1022600.0</v>
       </c>
       <c r="H4" t="n" s="0">
-        <v>834900.0</v>
+        <v>1124300.0</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>850100.0</v>
+        <v>866600.0</v>
       </c>
       <c r="J4" t="n" s="0">
-        <v>902900.0</v>
+        <v>829200.0</v>
       </c>
       <c r="K4" t="n" s="0">
-        <v>852100.0</v>
+        <v>823000.0</v>
       </c>
       <c r="L4" t="n" s="0">
-        <v>842000.0</v>
+        <v>1065500.0</v>
       </c>
       <c r="M4" t="n" s="0">
-        <v>822600.0</v>
+        <v>932400.0</v>
       </c>
       <c r="N4" t="n" s="0">
-        <v>821700.0</v>
+        <v>863600.0</v>
       </c>
       <c r="O4" t="n" s="0">
-        <v>856500.0</v>
+        <v>826700.0</v>
       </c>
       <c r="P4" t="n" s="0">
-        <v>827100.0</v>
+        <v>974300.0</v>
       </c>
       <c r="Q4" t="n" s="0">
-        <v>821900.0</v>
+        <v>834800.0</v>
       </c>
       <c r="R4" t="n" s="0">
-        <v>821600.0</v>
+        <v>1087300.0</v>
       </c>
       <c r="S4" t="n" s="0">
-        <v>826800.0</v>
+        <v>832100.0</v>
       </c>
       <c r="T4" t="n" s="0">
-        <v>835100.0</v>
+        <v>852300.0</v>
       </c>
       <c r="U4" t="n" s="0">
-        <v>830000.0</v>
+        <v>839100.0</v>
       </c>
       <c r="V4" t="n" s="0">
-        <v>868400.0</v>
+        <v>1186200.0</v>
       </c>
       <c r="W4" t="n" s="0">
-        <v>937045.0</v>
+        <v>942800.0</v>
       </c>
     </row>
     <row r="5">
@@ -435,67 +435,67 @@
         <v>1000.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>409500.0</v>
+        <v>57200.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>139300.0</v>
+        <v>92300.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>75700.0</v>
+        <v>56400.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>70300.0</v>
+        <v>35900.0</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>56100.0</v>
+        <v>36500.0</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>81300.0</v>
+        <v>75600.0</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>97700.0</v>
+        <v>42300.0</v>
       </c>
       <c r="J5" t="n" s="0">
-        <v>58900.0</v>
+        <v>56200.0</v>
       </c>
       <c r="K5" t="n" s="0">
-        <v>38400.0</v>
+        <v>41400.0</v>
       </c>
       <c r="L5" t="n" s="0">
-        <v>69300.0</v>
+        <v>37300.0</v>
       </c>
       <c r="M5" t="n" s="0">
-        <v>54400.0</v>
+        <v>60000.0</v>
       </c>
       <c r="N5" t="n" s="0">
-        <v>40700.0</v>
+        <v>55500.0</v>
       </c>
       <c r="O5" t="n" s="0">
-        <v>60600.0</v>
+        <v>35500.0</v>
       </c>
       <c r="P5" t="n" s="0">
-        <v>39400.0</v>
+        <v>75900.0</v>
       </c>
       <c r="Q5" t="n" s="0">
-        <v>49700.0</v>
+        <v>37300.0</v>
       </c>
       <c r="R5" t="n" s="0">
-        <v>50000.0</v>
+        <v>45200.0</v>
       </c>
       <c r="S5" t="n" s="0">
-        <v>38300.0</v>
+        <v>35100.0</v>
       </c>
       <c r="T5" t="n" s="0">
-        <v>37300.0</v>
+        <v>64900.0</v>
       </c>
       <c r="U5" t="n" s="0">
-        <v>38400.0</v>
+        <v>47600.0</v>
       </c>
       <c r="V5" t="n" s="0">
-        <v>40000.0</v>
+        <v>80300.0</v>
       </c>
       <c r="W5" t="n" s="0">
-        <v>77265.0</v>
+        <v>53420.0</v>
       </c>
     </row>
     <row r="6">
@@ -506,67 +506,67 @@
         <v>1000.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>324100.0</v>
+        <v>134300.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>77200.0</v>
+        <v>145200.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>133800.0</v>
+        <v>98200.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>130500.0</v>
+        <v>62400.0</v>
       </c>
       <c r="G6" t="n" s="0">
-        <v>79400.0</v>
+        <v>52400.0</v>
       </c>
       <c r="H6" t="n" s="0">
-        <v>81700.0</v>
+        <v>92200.0</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>106900.0</v>
+        <v>50400.0</v>
       </c>
       <c r="J6" t="n" s="0">
-        <v>58900.0</v>
+        <v>53600.0</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>77100.0</v>
+        <v>49000.0</v>
       </c>
       <c r="L6" t="n" s="0">
-        <v>88000.0</v>
+        <v>55100.0</v>
       </c>
       <c r="M6" t="n" s="0">
-        <v>50200.0</v>
+        <v>67500.0</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>91500.0</v>
+        <v>51900.0</v>
       </c>
       <c r="O6" t="n" s="0">
-        <v>70700.0</v>
+        <v>44400.0</v>
       </c>
       <c r="P6" t="n" s="0">
-        <v>47000.0</v>
+        <v>93100.0</v>
       </c>
       <c r="Q6" t="n" s="0">
-        <v>61300.0</v>
+        <v>46400.0</v>
       </c>
       <c r="R6" t="n" s="0">
-        <v>42100.0</v>
+        <v>47800.0</v>
       </c>
       <c r="S6" t="n" s="0">
-        <v>43900.0</v>
+        <v>42400.0</v>
       </c>
       <c r="T6" t="n" s="0">
-        <v>47100.0</v>
+        <v>69200.0</v>
       </c>
       <c r="U6" t="n" s="0">
-        <v>45500.0</v>
+        <v>45800.0</v>
       </c>
       <c r="V6" t="n" s="0">
-        <v>62800.0</v>
+        <v>94500.0</v>
       </c>
       <c r="W6" t="n" s="0">
-        <v>85985.0</v>
+        <v>69790.0</v>
       </c>
     </row>
   </sheetData>

--- a/excel/1000(n)/ReverseSort_Dataset.xlsx
+++ b/excel/1000(n)/ReverseSort_Dataset.xlsx
@@ -222,67 +222,67 @@
         <v>1000.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>314200.0</v>
+        <v>601700.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>351500.0</v>
+        <v>305500.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>669700.0</v>
+        <v>305200.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>598900.0</v>
+        <v>316700.0</v>
       </c>
       <c r="G2" t="n" s="0">
-        <v>594800.0</v>
+        <v>321500.0</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>606300.0</v>
+        <v>630800.0</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>665200.0</v>
+        <v>329100.0</v>
       </c>
       <c r="J2" t="n" s="0">
-        <v>594700.0</v>
+        <v>686800.0</v>
       </c>
       <c r="K2" t="n" s="0">
-        <v>594600.0</v>
+        <v>722900.0</v>
       </c>
       <c r="L2" t="n" s="0">
-        <v>651900.0</v>
+        <v>614900.0</v>
       </c>
       <c r="M2" t="n" s="0">
-        <v>594500.0</v>
+        <v>601000.0</v>
       </c>
       <c r="N2" t="n" s="0">
-        <v>332000.0</v>
+        <v>733800.0</v>
       </c>
       <c r="O2" t="n" s="0">
-        <v>612100.0</v>
+        <v>596100.0</v>
       </c>
       <c r="P2" t="n" s="0">
-        <v>608300.0</v>
+        <v>592900.0</v>
       </c>
       <c r="Q2" t="n" s="0">
-        <v>606400.0</v>
+        <v>600100.0</v>
       </c>
       <c r="R2" t="n" s="0">
-        <v>647200.0</v>
+        <v>613800.0</v>
       </c>
       <c r="S2" t="n" s="0">
-        <v>818200.0</v>
+        <v>600200.0</v>
       </c>
       <c r="T2" t="n" s="0">
-        <v>598300.0</v>
+        <v>603000.0</v>
       </c>
       <c r="U2" t="n" s="0">
-        <v>594200.0</v>
+        <v>595000.0</v>
       </c>
       <c r="V2" t="n" s="0">
-        <v>642800.0</v>
+        <v>330100.0</v>
       </c>
       <c r="W2" t="n" s="0">
-        <v>584790.0</v>
+        <v>535055.0</v>
       </c>
     </row>
     <row r="3">
@@ -293,67 +293,67 @@
         <v>1000.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>93100.0</v>
+        <v>168200.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>160000.0</v>
+        <v>185300.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>150700.0</v>
+        <v>203800.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>84900.0</v>
+        <v>182000.0</v>
       </c>
       <c r="G3" t="n" s="0">
-        <v>86100.0</v>
+        <v>120600.0</v>
       </c>
       <c r="H3" t="n" s="0">
-        <v>91100.0</v>
+        <v>186000.0</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>118500.0</v>
+        <v>89800.0</v>
       </c>
       <c r="J3" t="n" s="0">
-        <v>87400.0</v>
+        <v>85300.0</v>
       </c>
       <c r="K3" t="n" s="0">
-        <v>87200.0</v>
+        <v>160500.0</v>
       </c>
       <c r="L3" t="n" s="0">
-        <v>87400.0</v>
+        <v>88200.0</v>
       </c>
       <c r="M3" t="n" s="0">
-        <v>88400.0</v>
+        <v>89700.0</v>
       </c>
       <c r="N3" t="n" s="0">
-        <v>109700.0</v>
+        <v>85900.0</v>
       </c>
       <c r="O3" t="n" s="0">
-        <v>89300.0</v>
+        <v>85800.0</v>
       </c>
       <c r="P3" t="n" s="0">
-        <v>85200.0</v>
+        <v>89600.0</v>
       </c>
       <c r="Q3" t="n" s="0">
-        <v>87700.0</v>
+        <v>85700.0</v>
       </c>
       <c r="R3" t="n" s="0">
-        <v>181800.0</v>
+        <v>124000.0</v>
       </c>
       <c r="S3" t="n" s="0">
-        <v>87600.0</v>
+        <v>86800.0</v>
       </c>
       <c r="T3" t="n" s="0">
-        <v>92700.0</v>
+        <v>187800.0</v>
       </c>
       <c r="U3" t="n" s="0">
-        <v>87200.0</v>
+        <v>89600.0</v>
       </c>
       <c r="V3" t="n" s="0">
-        <v>97100.0</v>
+        <v>181900.0</v>
       </c>
       <c r="W3" t="n" s="0">
-        <v>102655.0</v>
+        <v>128825.0</v>
       </c>
     </row>
     <row r="4">
@@ -364,67 +364,67 @@
         <v>1000.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>1172800.0</v>
+        <v>843600.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>896500.0</v>
+        <v>1091800.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>995600.0</v>
+        <v>1125900.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>831100.0</v>
+        <v>1023200.0</v>
       </c>
       <c r="G4" t="n" s="0">
-        <v>1022600.0</v>
+        <v>823000.0</v>
       </c>
       <c r="H4" t="n" s="0">
-        <v>1124300.0</v>
+        <v>1123400.0</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>866600.0</v>
+        <v>846400.0</v>
       </c>
       <c r="J4" t="n" s="0">
-        <v>829200.0</v>
+        <v>857700.0</v>
       </c>
       <c r="K4" t="n" s="0">
-        <v>823000.0</v>
+        <v>858300.0</v>
       </c>
       <c r="L4" t="n" s="0">
-        <v>1065500.0</v>
+        <v>1003600.0</v>
       </c>
       <c r="M4" t="n" s="0">
-        <v>932400.0</v>
+        <v>1132400.0</v>
       </c>
       <c r="N4" t="n" s="0">
-        <v>863600.0</v>
+        <v>842500.0</v>
       </c>
       <c r="O4" t="n" s="0">
-        <v>826700.0</v>
+        <v>861900.0</v>
       </c>
       <c r="P4" t="n" s="0">
-        <v>974300.0</v>
+        <v>827400.0</v>
       </c>
       <c r="Q4" t="n" s="0">
-        <v>834800.0</v>
+        <v>910300.0</v>
       </c>
       <c r="R4" t="n" s="0">
-        <v>1087300.0</v>
+        <v>824900.0</v>
       </c>
       <c r="S4" t="n" s="0">
-        <v>832100.0</v>
+        <v>826800.0</v>
       </c>
       <c r="T4" t="n" s="0">
-        <v>852300.0</v>
+        <v>1127400.0</v>
       </c>
       <c r="U4" t="n" s="0">
-        <v>839100.0</v>
+        <v>825900.0</v>
       </c>
       <c r="V4" t="n" s="0">
-        <v>1186200.0</v>
+        <v>1152300.0</v>
       </c>
       <c r="W4" t="n" s="0">
-        <v>942800.0</v>
+        <v>946435.0</v>
       </c>
     </row>
     <row r="5">
@@ -435,67 +435,67 @@
         <v>1000.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>57200.0</v>
+        <v>93900.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>92300.0</v>
+        <v>76800.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>56400.0</v>
+        <v>259500.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>35900.0</v>
+        <v>68900.0</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>36500.0</v>
+        <v>39500.0</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>75600.0</v>
+        <v>5194800.0</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>42300.0</v>
+        <v>39100.0</v>
       </c>
       <c r="J5" t="n" s="0">
-        <v>56200.0</v>
+        <v>38400.0</v>
       </c>
       <c r="K5" t="n" s="0">
-        <v>41400.0</v>
+        <v>40200.0</v>
       </c>
       <c r="L5" t="n" s="0">
-        <v>37300.0</v>
+        <v>91200.0</v>
       </c>
       <c r="M5" t="n" s="0">
-        <v>60000.0</v>
+        <v>89000.0</v>
       </c>
       <c r="N5" t="n" s="0">
-        <v>55500.0</v>
+        <v>52700.0</v>
       </c>
       <c r="O5" t="n" s="0">
-        <v>35500.0</v>
+        <v>36900.0</v>
       </c>
       <c r="P5" t="n" s="0">
-        <v>75900.0</v>
+        <v>39500.0</v>
       </c>
       <c r="Q5" t="n" s="0">
-        <v>37300.0</v>
+        <v>46100.0</v>
       </c>
       <c r="R5" t="n" s="0">
-        <v>45200.0</v>
+        <v>61900.0</v>
       </c>
       <c r="S5" t="n" s="0">
-        <v>35100.0</v>
+        <v>36000.0</v>
       </c>
       <c r="T5" t="n" s="0">
-        <v>64900.0</v>
+        <v>43900.0</v>
       </c>
       <c r="U5" t="n" s="0">
-        <v>47600.0</v>
+        <v>40100.0</v>
       </c>
       <c r="V5" t="n" s="0">
-        <v>80300.0</v>
+        <v>84200.0</v>
       </c>
       <c r="W5" t="n" s="0">
-        <v>53420.0</v>
+        <v>323630.0</v>
       </c>
     </row>
     <row r="6">
@@ -506,67 +506,67 @@
         <v>1000.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>134300.0</v>
+        <v>125200.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>145200.0</v>
+        <v>97700.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>98200.0</v>
+        <v>62300.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>62400.0</v>
+        <v>104600.0</v>
       </c>
       <c r="G6" t="n" s="0">
-        <v>52400.0</v>
+        <v>107000.0</v>
       </c>
       <c r="H6" t="n" s="0">
-        <v>92200.0</v>
+        <v>63200.0</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>50400.0</v>
+        <v>60500.0</v>
       </c>
       <c r="J6" t="n" s="0">
-        <v>53600.0</v>
+        <v>44500.0</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>49000.0</v>
+        <v>46700.0</v>
       </c>
       <c r="L6" t="n" s="0">
-        <v>55100.0</v>
+        <v>46400.0</v>
       </c>
       <c r="M6" t="n" s="0">
-        <v>67500.0</v>
+        <v>52200.0</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>51900.0</v>
+        <v>94200.0</v>
       </c>
       <c r="O6" t="n" s="0">
-        <v>44400.0</v>
+        <v>50900.0</v>
       </c>
       <c r="P6" t="n" s="0">
-        <v>93100.0</v>
+        <v>44500.0</v>
       </c>
       <c r="Q6" t="n" s="0">
-        <v>46400.0</v>
+        <v>60400.0</v>
       </c>
       <c r="R6" t="n" s="0">
-        <v>47800.0</v>
+        <v>44100.0</v>
       </c>
       <c r="S6" t="n" s="0">
-        <v>42400.0</v>
+        <v>51500.0</v>
       </c>
       <c r="T6" t="n" s="0">
-        <v>69200.0</v>
+        <v>44700.0</v>
       </c>
       <c r="U6" t="n" s="0">
-        <v>45800.0</v>
+        <v>116700.0</v>
       </c>
       <c r="V6" t="n" s="0">
-        <v>94500.0</v>
+        <v>83400.0</v>
       </c>
       <c r="W6" t="n" s="0">
-        <v>69790.0</v>
+        <v>70035.0</v>
       </c>
     </row>
   </sheetData>
